--- a/bajada_zonales.xlsx
+++ b/bajada_zonales.xlsx
@@ -421,10 +421,10 @@
         <v>16</v>
       </c>
       <c r="C1" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1" t="n">
         <v>20</v>
-      </c>
-      <c r="D1" t="n">
-        <v>15</v>
       </c>
       <c r="E1" t="n">
         <v>8</v>
@@ -436,10 +436,10 @@
         <v>19</v>
       </c>
       <c r="H1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I1" t="n">
         <v>3</v>
-      </c>
-      <c r="I1" t="n">
-        <v>13</v>
       </c>
       <c r="J1" t="n">
         <v>0</v>
@@ -448,37 +448,37 @@
         <v>18</v>
       </c>
       <c r="L1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M1" t="n">
         <v>9</v>
       </c>
       <c r="N1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O1" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1" t="n">
         <v>5</v>
       </c>
-      <c r="P1" t="n">
-        <v>14</v>
-      </c>
       <c r="Q1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R1" t="n">
         <v>1</v>
       </c>
       <c r="S1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T1" t="n">
         <v>12</v>
       </c>
       <c r="U1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V1" t="n">
         <v>17</v>
-      </c>
-      <c r="V1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -494,14 +494,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>SAN FERNANDO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>VIÑA DEL MAR</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SAN FERNANDO</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>LA SERENA</t>
@@ -519,14 +519,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>RANCAGUA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>CHILLAN</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>RANCAGUA</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>ANTOFAGASTA</t>
@@ -539,44 +539,44 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>OSORNO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>IQUIQUE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>OSORNO</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>COPIAPO</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SAN FELIPE</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ARICA</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>CALAMA</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>ARICA</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>PUERTO MONTT</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>PUNTA ARENAS</t>
@@ -584,12 +584,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>COYHAYQUE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>Sin zonal</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>COYHAYQUE</t>
         </is>
       </c>
     </row>
@@ -600,67 +600,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17284051533</v>
+        <v>22553741817</v>
       </c>
       <c r="C3" t="n">
-        <v>3262610383</v>
+        <v>4910449462</v>
       </c>
       <c r="D3" t="n">
-        <v>2725853142</v>
+        <v>4005614430</v>
       </c>
       <c r="E3" t="n">
-        <v>2685268242</v>
+        <v>3773281666</v>
       </c>
       <c r="F3" t="n">
-        <v>2256060450</v>
+        <v>3144398701</v>
       </c>
       <c r="G3" t="n">
-        <v>2224284305</v>
+        <v>3074718637</v>
       </c>
       <c r="H3" t="n">
-        <v>1922748118</v>
+        <v>2734829079</v>
       </c>
       <c r="I3" t="n">
-        <v>1916382715</v>
+        <v>2476221306</v>
       </c>
       <c r="J3" t="n">
-        <v>1866875600</v>
+        <v>2193958524</v>
       </c>
       <c r="K3" t="n">
-        <v>1527749310</v>
+        <v>1904266689</v>
       </c>
       <c r="L3" t="n">
-        <v>1391544725</v>
+        <v>1802213960</v>
       </c>
       <c r="M3" t="n">
-        <v>1390889018</v>
+        <v>1742192409</v>
       </c>
       <c r="N3" t="n">
-        <v>1302937056</v>
+        <v>1649046282</v>
       </c>
       <c r="O3" t="n">
-        <v>1292218294</v>
+        <v>1598443382</v>
       </c>
       <c r="P3" t="n">
-        <v>1003067636</v>
+        <v>1458627862</v>
       </c>
       <c r="Q3" t="n">
-        <v>918602927</v>
+        <v>1191809027</v>
       </c>
       <c r="R3" t="n">
-        <v>885576169</v>
+        <v>1162007839</v>
       </c>
       <c r="S3" t="n">
-        <v>767398496</v>
+        <v>1135998082</v>
       </c>
       <c r="T3" t="n">
-        <v>532171061</v>
+        <v>740291589</v>
       </c>
       <c r="U3" t="n">
-        <v>200782675</v>
+        <v>378960835</v>
       </c>
       <c r="V3" t="n">
-        <v>190404553</v>
+        <v>280014911</v>
       </c>
     </row>
     <row r="4">
@@ -670,67 +670,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3533514014.588236</v>
+        <v>4626095480.144089</v>
       </c>
       <c r="C4" t="n">
-        <v>654495398.9450512</v>
+        <v>883513960.5768543</v>
       </c>
       <c r="D4" t="n">
-        <v>486820910.9122928</v>
+        <v>810511120.1588317</v>
       </c>
       <c r="E4" t="n">
-        <v>524236783.5808255</v>
+        <v>742362565.8148775</v>
       </c>
       <c r="F4" t="n">
-        <v>419522970.7117081</v>
+        <v>577141248.4788522</v>
       </c>
       <c r="G4" t="n">
-        <v>412941437.5157632</v>
+        <v>565879853.5124972</v>
       </c>
       <c r="H4" t="n">
-        <v>357032769.1382127</v>
+        <v>511713625.6094597</v>
       </c>
       <c r="I4" t="n">
-        <v>358590241.7904754</v>
+        <v>462022460.4757701</v>
       </c>
       <c r="J4" t="n">
-        <v>354125010.7611983</v>
+        <v>418813707.4057584</v>
       </c>
       <c r="K4" t="n">
-        <v>268013576.2724107</v>
+        <v>339676435.5574799</v>
       </c>
       <c r="L4" t="n">
-        <v>316975454.9544364</v>
+        <v>359067593.4019247</v>
       </c>
       <c r="M4" t="n">
-        <v>249984622.9130609</v>
+        <v>315060891.3802796</v>
       </c>
       <c r="N4" t="n">
-        <v>267983219.4905262</v>
+        <v>369697008.2359885</v>
       </c>
       <c r="O4" t="n">
-        <v>221448782.4969345</v>
+        <v>297297081.0176763</v>
       </c>
       <c r="P4" t="n">
-        <v>182483806.1185161</v>
+        <v>251173020.1459699</v>
       </c>
       <c r="Q4" t="n">
-        <v>203446222.8847862</v>
+        <v>197203589.657272</v>
       </c>
       <c r="R4" t="n">
-        <v>190936855.7037342</v>
+        <v>245087854.4035765</v>
       </c>
       <c r="S4" t="n">
-        <v>123333136.6172599</v>
+        <v>245419596.9312054</v>
       </c>
       <c r="T4" t="n">
-        <v>95755969.84194566</v>
+        <v>138379738.6616906</v>
       </c>
       <c r="U4" t="n">
-        <v>35439553.06135596</v>
+        <v>60916894.53103108</v>
       </c>
       <c r="V4" t="n">
-        <v>31403381.21297439</v>
+        <v>50418145.65678468</v>
       </c>
     </row>
     <row r="5">
@@ -740,67 +740,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2044378314796035</v>
+        <v>0.205114322832992</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2006048292972196</v>
+        <v>0.1799252731168531</v>
       </c>
       <c r="D5" t="n">
-        <v>0.178593961432238</v>
+        <v>0.2023437688082304</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1952269703939788</v>
+        <v>0.1967418898260636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1859537809422208</v>
+        <v>0.1835458233382765</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1856513740565927</v>
+        <v>0.18404280856886</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1856887887684375</v>
+        <v>0.1871099110137331</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1871182822636111</v>
+        <v>0.1865836705936857</v>
       </c>
       <c r="J5" t="n">
-        <v>0.189688595619975</v>
+        <v>0.1908940861116107</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1754303369787879</v>
+        <v>0.178376504467374</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2277867532819949</v>
+        <v>0.1992369393265185</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1797301004450528</v>
+        <v>0.1808416164326656</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2056762590767287</v>
+        <v>0.2241883761974295</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1713710319109091</v>
+        <v>0.1859916243299735</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1819257242175802</v>
+        <v>0.1721981505286576</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2214735190853427</v>
+        <v>0.1654657627100453</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2156074907925105</v>
+        <v>0.2109175568165651</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1607158956658418</v>
+        <v>0.2160387423358391</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1799345677722706</v>
+        <v>0.1869259906743187</v>
       </c>
       <c r="U5" t="n">
-        <v>0.176507027119526</v>
+        <v>0.1607472036814334</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1649297809226988</v>
+        <v>0.1800552173337108</v>
       </c>
     </row>
     <row r="6">
@@ -813,10 +813,10 @@
         <v>438856</v>
       </c>
       <c r="C6" t="n">
+        <v>75585</v>
+      </c>
+      <c r="D6" t="n">
         <v>334871</v>
-      </c>
-      <c r="D6" t="n">
-        <v>75585</v>
       </c>
       <c r="E6" t="n">
         <v>250141</v>
@@ -828,10 +828,10 @@
         <v>292518</v>
       </c>
       <c r="H6" t="n">
+        <v>257744</v>
+      </c>
+      <c r="I6" t="n">
         <v>190382</v>
-      </c>
-      <c r="I6" t="n">
-        <v>257744</v>
       </c>
       <c r="J6" t="n">
         <v>401096</v>
@@ -840,36 +840,36 @@
         <v>232131</v>
       </c>
       <c r="L6" t="n">
-        <v>199587</v>
+        <v>166455</v>
       </c>
       <c r="M6" t="n">
         <v>219441</v>
       </c>
       <c r="N6" t="n">
-        <v>166455</v>
+        <v>199587</v>
       </c>
       <c r="O6" t="n">
+        <v>80413</v>
+      </c>
+      <c r="P6" t="n">
         <v>168831</v>
       </c>
-      <c r="P6" t="n">
-        <v>80413</v>
-      </c>
       <c r="Q6" t="n">
-        <v>166334</v>
+        <v>277040</v>
       </c>
       <c r="R6" t="n">
         <v>241653</v>
       </c>
       <c r="S6" t="n">
-        <v>277040</v>
+        <v>166334</v>
       </c>
       <c r="T6" t="n">
         <v>132363</v>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
+      <c r="U6" t="n">
         <v>57823</v>
       </c>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -878,66 +878,66 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39384.33457216035</v>
+        <v>51392.12365103816</v>
       </c>
       <c r="C7" t="n">
-        <v>9742.887210298892</v>
+        <v>64965.92527617914</v>
       </c>
       <c r="D7" t="n">
-        <v>36063.41393133558</v>
+        <v>11961.66413335284</v>
       </c>
       <c r="E7" t="n">
-        <v>10735.01841761247</v>
+        <v>15084.61893891845</v>
       </c>
       <c r="F7" t="n">
-        <v>9792.9916440586</v>
+        <v>13649.04482257189</v>
       </c>
       <c r="G7" t="n">
-        <v>7603.92285261078</v>
+        <v>10511.21174423454</v>
       </c>
       <c r="H7" t="n">
-        <v>10099.42178357198</v>
+        <v>10610.64109736793</v>
       </c>
       <c r="I7" t="n">
-        <v>7435.217560835557</v>
+        <v>13006.59361704363</v>
       </c>
       <c r="J7" t="n">
-        <v>4654.435845782556</v>
+        <v>5469.908759997606</v>
       </c>
       <c r="K7" t="n">
-        <v>6581.410108947103</v>
+        <v>8203.413973144474</v>
       </c>
       <c r="L7" t="n">
-        <v>6972.121054978531</v>
+        <v>10827.03409329849</v>
       </c>
       <c r="M7" t="n">
-        <v>6338.327924134505</v>
+        <v>7939.229264358073</v>
       </c>
       <c r="N7" t="n">
-        <v>7827.563341443633</v>
+        <v>8262.293045138211</v>
       </c>
       <c r="O7" t="n">
-        <v>7653.916010685241</v>
+        <v>19877.92250009327</v>
       </c>
       <c r="P7" t="n">
-        <v>12473.94868988845</v>
+        <v>8639.573668342899</v>
       </c>
       <c r="Q7" t="n">
-        <v>5522.640752942874</v>
+        <v>4301.93844571181</v>
       </c>
       <c r="R7" t="n">
-        <v>3664.660355964958</v>
+        <v>4808.580232813166</v>
       </c>
       <c r="S7" t="n">
-        <v>2769.991683511406</v>
+        <v>6829.620414347037</v>
       </c>
       <c r="T7" t="n">
-        <v>4020.542455217848</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>3292.886100686578</v>
-      </c>
+        <v>5592.889168423199</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6553.807913805925</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
